--- a/backstage_llm/noblank-newtokenize/test_result.xlsx
+++ b/backstage_llm/noblank-newtokenize/test_result.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28760" windowHeight="15300"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="16">
   <si>
     <t>all vs full</t>
   </si>
@@ -73,35 +73,24 @@
   <si>
     <t>0.7000000000000011</t>
   </si>
+  <si>
+    <t>college_medicine</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF098658"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -556,19 +545,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -577,139 +575,124 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
@@ -1239,13 +1222,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="7"/>
+  <dimension ref="A1:H25"/>
+  <sheetFormatPr defaultColWidth="9.22727272727273" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="29.6153846153846" customWidth="1"/>
-    <col min="3" max="3" width="11.0769230769231" customWidth="1"/>
-    <col min="4" max="4" width="13.2307692307692" customWidth="1"/>
-    <col min="5" max="5" width="20.2307692307692" customWidth="1"/>
+    <col min="1" max="1" width="29.6181818181818" customWidth="1"/>
+    <col min="3" max="3" width="11.0727272727273" customWidth="1"/>
+    <col min="4" max="4" width="13.2272727272727" customWidth="1"/>
+    <col min="5" max="5" width="20.2272727272727" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1277,16 +1260,16 @@
       <c r="B4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4">
         <v>9</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4">
         <v>8</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4">
         <v>14.1</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4">
         <v>-30.7999999999999</v>
       </c>
     </row>
@@ -1294,16 +1277,16 @@
       <c r="B5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5">
         <v>13</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5">
         <v>10</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5">
         <v>21.0999999999999</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5">
         <v>-32.2</v>
       </c>
     </row>
@@ -1311,16 +1294,16 @@
       <c r="B6" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6">
         <v>16</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6">
         <v>8</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6">
         <v>21.5999999999999</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6">
         <v>-29.2</v>
       </c>
     </row>
@@ -1347,16 +1330,16 @@
       <c r="B10" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10">
         <v>4</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10">
         <v>5</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10">
         <v>2.09999999999999</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10">
         <v>-3.29999999999999</v>
       </c>
     </row>
@@ -1364,16 +1347,16 @@
       <c r="B11" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11">
         <v>3</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11">
         <v>5</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11">
         <v>1.59999999999999</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11">
         <v>-3.79999999999999</v>
       </c>
     </row>
@@ -1381,16 +1364,16 @@
       <c r="B12" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12">
         <v>11</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12">
         <v>9</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12">
         <v>50.8</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12">
         <v>-28.5</v>
       </c>
     </row>
@@ -1417,16 +1400,16 @@
       <c r="B16" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16">
         <v>11</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16">
         <v>11</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16">
         <v>34.2</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16">
         <v>-20.5</v>
       </c>
     </row>
@@ -1434,16 +1417,16 @@
       <c r="B17" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17">
         <v>14</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17">
         <v>12</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17">
         <v>36.9</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17">
         <v>-32.9</v>
       </c>
     </row>
@@ -1476,11 +1459,47 @@
       <c r="D21">
         <v>8</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F21">
         <v>-12.7999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="3:6">
+      <c r="C24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25">
+        <v>6</v>
+      </c>
+      <c r="D25">
+        <v>9</v>
+      </c>
+      <c r="E25">
+        <v>11.7</v>
+      </c>
+      <c r="F25">
+        <v>-15.3</v>
       </c>
     </row>
   </sheetData>

--- a/backstage_llm/noblank-newtokenize/test_result.xlsx
+++ b/backstage_llm/noblank-newtokenize/test_result.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="28760" windowHeight="15300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="18">
   <si>
     <t>all vs full</t>
   </si>
@@ -75,6 +75,12 @@
   </si>
   <si>
     <t>college_medicine</t>
+  </si>
+  <si>
+    <t>international_law</t>
+  </si>
+  <si>
+    <t>10.999999999999996</t>
   </si>
 </sst>
 </file>
@@ -82,10 +88,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -545,19 +551,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1222,13 +1228,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultColWidth="9.22727272727273" defaultRowHeight="14" outlineLevelCol="7"/>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="29.6181818181818" customWidth="1"/>
-    <col min="3" max="3" width="11.0727272727273" customWidth="1"/>
-    <col min="4" max="4" width="13.2272727272727" customWidth="1"/>
-    <col min="5" max="5" width="20.2272727272727" customWidth="1"/>
+    <col min="1" max="1" width="29.6153846153846" customWidth="1"/>
+    <col min="3" max="3" width="11.0769230769231" customWidth="1"/>
+    <col min="4" max="4" width="13.2307692307692" customWidth="1"/>
+    <col min="5" max="5" width="20.2307692307692" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1502,6 +1508,42 @@
         <v>-15.3</v>
       </c>
     </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="3:6">
+      <c r="C28" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" t="s">
+        <v>3</v>
+      </c>
+      <c r="E28" t="s">
+        <v>4</v>
+      </c>
+      <c r="F28" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29">
+        <v>15</v>
+      </c>
+      <c r="D29">
+        <v>16</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29">
+        <v>-14.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/backstage_llm/noblank-newtokenize/test_result.xlsx
+++ b/backstage_llm/noblank-newtokenize/test_result.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="22">
   <si>
     <t>all vs full</t>
   </si>
@@ -68,10 +68,22 @@
     <t>college_biology</t>
   </si>
   <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
     <t>high_school_geography</t>
   </si>
   <si>
+    <t>size</t>
+  </si>
+  <si>
+    <t>full</t>
+  </si>
+  <si>
     <t>0.7000000000000011</t>
+  </si>
+  <si>
+    <t>0.6000000000000014</t>
   </si>
   <si>
     <t>college_medicine</t>
@@ -1228,8 +1240,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H29"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="7"/>
+  <dimension ref="A1:I31"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="29.6153846153846" customWidth="1"/>
     <col min="3" max="3" width="11.0769230769231" customWidth="1"/>
@@ -1409,8 +1421,8 @@
       <c r="C16">
         <v>11</v>
       </c>
-      <c r="D16">
-        <v>11</v>
+      <c r="D16" t="s">
+        <v>13</v>
       </c>
       <c r="E16">
         <v>34.2</v>
@@ -1436,12 +1448,15 @@
         <v>-32.9</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="3:6">
+        <v>14</v>
+      </c>
+      <c r="I19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="3:9">
       <c r="C20" t="s">
         <v>2</v>
       </c>
@@ -1454,8 +1469,14 @@
       <c r="F20" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="2:6">
+      <c r="H20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20">
+        <v>22475</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9">
       <c r="B21" t="s">
         <v>6</v>
       </c>
@@ -1466,81 +1487,110 @@
         <v>8</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F21">
         <v>-12.7999999999999</v>
       </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
+      <c r="H21" t="s">
+        <v>6</v>
+      </c>
+      <c r="I21">
+        <v>21961</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9">
+      <c r="B22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22">
+        <v>3</v>
+      </c>
+      <c r="D22">
+        <v>9</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22">
+        <v>-20.9999999999999</v>
+      </c>
+      <c r="H22" t="s">
+        <v>10</v>
+      </c>
+      <c r="I22">
+        <v>20804</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="3:6">
+      <c r="C26" t="s">
+        <v>2</v>
+      </c>
+      <c r="D26" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" t="s">
+        <v>4</v>
+      </c>
+      <c r="F26" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="B27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27">
+        <v>6</v>
+      </c>
+      <c r="D27">
+        <v>9</v>
+      </c>
+      <c r="E27">
+        <v>11.7</v>
+      </c>
+      <c r="F27">
+        <v>-15.3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="3:6">
+      <c r="C30" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" t="s">
+        <v>3</v>
+      </c>
+      <c r="E30" t="s">
+        <v>4</v>
+      </c>
+      <c r="F30" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31">
         <v>15</v>
       </c>
-    </row>
-    <row r="24" spans="3:6">
-      <c r="C24" t="s">
-        <v>2</v>
-      </c>
-      <c r="D24" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F24" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6">
-      <c r="B25" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25">
-        <v>6</v>
-      </c>
-      <c r="D25">
-        <v>9</v>
-      </c>
-      <c r="E25">
-        <v>11.7</v>
-      </c>
-      <c r="F25">
-        <v>-15.3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
+      <c r="D31">
         <v>16</v>
       </c>
-    </row>
-    <row r="28" spans="3:6">
-      <c r="C28" t="s">
-        <v>2</v>
-      </c>
-      <c r="D28" t="s">
-        <v>3</v>
-      </c>
-      <c r="E28" t="s">
-        <v>4</v>
-      </c>
-      <c r="F28" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6">
-      <c r="B29" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29">
-        <v>15</v>
-      </c>
-      <c r="D29">
-        <v>16</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F29">
+      <c r="E31" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31">
         <v>-14.7</v>
       </c>
     </row>

--- a/backstage_llm/noblank-newtokenize/test_result.xlsx
+++ b/backstage_llm/noblank-newtokenize/test_result.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="26">
   <si>
     <t>all vs full</t>
   </si>
@@ -68,31 +68,43 @@
     <t>college_biology</t>
   </si>
   <si>
+    <t>size</t>
+  </si>
+  <si>
+    <t>full</t>
+  </si>
+  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>high_school_geography</t>
   </si>
   <si>
-    <t>size</t>
-  </si>
-  <si>
-    <t>full</t>
-  </si>
-  <si>
     <t>0.7000000000000011</t>
   </si>
   <si>
     <t>0.6000000000000014</t>
   </si>
   <si>
+    <t>bm80</t>
+  </si>
+  <si>
     <t>college_medicine</t>
   </si>
   <si>
+    <t>17.999999999999996</t>
+  </si>
+  <si>
     <t>international_law</t>
   </si>
   <si>
     <t>10.999999999999996</t>
+  </si>
+  <si>
+    <t>18.799999999999997</t>
+  </si>
+  <si>
+    <t>high_school_biology</t>
   </si>
 </sst>
 </file>
@@ -105,13 +117,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.75"/>
+      <color theme="1"/>
+      <name val="Menlo"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -578,142 +596,148 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1240,7 +1264,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="29.6153846153846" customWidth="1"/>
@@ -1395,12 +1419,15 @@
         <v>-28.5</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="15" spans="3:6">
+      <c r="I14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="3:8">
       <c r="C15" t="s">
         <v>2</v>
       </c>
@@ -1413,8 +1440,11 @@
       <c r="F15" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="2:6">
+      <c r="H15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8">
       <c r="B16" t="s">
         <v>6</v>
       </c>
@@ -1422,13 +1452,16 @@
         <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E16">
         <v>34.2</v>
       </c>
       <c r="F16">
         <v>-20.5</v>
+      </c>
+      <c r="H16" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="2:6">
@@ -1450,10 +1483,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I19" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="3:9">
@@ -1470,7 +1503,7 @@
         <v>5</v>
       </c>
       <c r="H20" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I20">
         <v>22475</v>
@@ -1486,7 +1519,7 @@
       <c r="D21">
         <v>8</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F21">
@@ -1509,7 +1542,7 @@
       <c r="D22">
         <v>9</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F22">
@@ -1522,12 +1555,26 @@
         <v>20804</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="23" spans="2:9">
+      <c r="B23" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" t="s">
+        <v>19</v>
+      </c>
+      <c r="I23">
+        <v>16174</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" spans="3:6">
+        <v>20</v>
+      </c>
+      <c r="I25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="3:9">
       <c r="C26" t="s">
         <v>2</v>
       </c>
@@ -1540,8 +1587,14 @@
       <c r="F26" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="2:6">
+      <c r="H26" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26">
+        <v>19999</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9">
       <c r="B27" t="s">
         <v>6</v>
       </c>
@@ -1557,41 +1610,225 @@
       <c r="F27">
         <v>-15.3</v>
       </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30" spans="3:6">
-      <c r="C30" t="s">
+      <c r="H27" t="s">
+        <v>6</v>
+      </c>
+      <c r="I27">
+        <v>14804</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9">
+      <c r="B28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28">
+        <v>9</v>
+      </c>
+      <c r="D28">
+        <v>7</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28">
+        <v>-21.8</v>
+      </c>
+      <c r="H28" t="s">
+        <v>10</v>
+      </c>
+      <c r="I28">
+        <v>12010</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9">
+      <c r="B29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29">
+        <v>9</v>
+      </c>
+      <c r="D29">
+        <v>6</v>
+      </c>
+      <c r="E29">
+        <v>21.1</v>
+      </c>
+      <c r="F29">
+        <v>-27.2</v>
+      </c>
+      <c r="H29" t="s">
+        <v>19</v>
+      </c>
+      <c r="I29">
+        <v>8572</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8">
+      <c r="B30" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>22</v>
+      </c>
+      <c r="I32" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9">
+      <c r="C33" t="s">
         <v>2</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D33" t="s">
         <v>3</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E33" t="s">
         <v>4</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F33" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="31" spans="2:6">
-      <c r="B31" t="s">
+      <c r="H33" t="s">
+        <v>14</v>
+      </c>
+      <c r="I33">
+        <v>13791</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9">
+      <c r="B34" t="s">
         <v>6</v>
       </c>
-      <c r="C31">
+      <c r="C34">
         <v>15</v>
       </c>
-      <c r="D31">
+      <c r="D34">
         <v>16</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31">
+      <c r="E34" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F34">
         <v>-14.7</v>
+      </c>
+      <c r="H34" t="s">
+        <v>6</v>
+      </c>
+      <c r="I34">
+        <v>12996</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9">
+      <c r="B35" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35">
+        <v>15</v>
+      </c>
+      <c r="D35">
+        <v>19</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F35">
+        <v>-41.3999999999999</v>
+      </c>
+      <c r="H35" t="s">
+        <v>10</v>
+      </c>
+      <c r="I35">
+        <v>11284</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9">
+      <c r="B36" t="s">
+        <v>19</v>
+      </c>
+      <c r="H36" t="s">
+        <v>19</v>
+      </c>
+      <c r="I36">
+        <v>7562</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" t="s">
+        <v>25</v>
+      </c>
+      <c r="I38" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="3:9">
+      <c r="C39" t="s">
+        <v>2</v>
+      </c>
+      <c r="D39" t="s">
+        <v>3</v>
+      </c>
+      <c r="E39" t="s">
+        <v>4</v>
+      </c>
+      <c r="F39" t="s">
+        <v>5</v>
+      </c>
+      <c r="H39" t="s">
+        <v>14</v>
+      </c>
+      <c r="I39">
+        <v>34556</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9">
+      <c r="B40" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40"/>
+      <c r="D40"/>
+      <c r="E40"/>
+      <c r="F40"/>
+      <c r="H40" t="s">
+        <v>6</v>
+      </c>
+      <c r="I40">
+        <v>26342</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8">
+      <c r="B41" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41"/>
+      <c r="D41"/>
+      <c r="E41"/>
+      <c r="F41"/>
+      <c r="H41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8">
+      <c r="B42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C42"/>
+      <c r="D42"/>
+      <c r="E42"/>
+      <c r="F42"/>
+      <c r="H42" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8">
+      <c r="B43" t="s">
+        <v>11</v>
+      </c>
+      <c r="H43" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/backstage_llm/noblank-newtokenize/test_result.xlsx
+++ b/backstage_llm/noblank-newtokenize/test_result.xlsx
@@ -1788,10 +1788,18 @@
       <c r="B40" t="s">
         <v>6</v>
       </c>
-      <c r="C40"/>
-      <c r="D40"/>
-      <c r="E40"/>
-      <c r="F40"/>
+      <c r="C40">
+        <v>8</v>
+      </c>
+      <c r="D40">
+        <v>11</v>
+      </c>
+      <c r="E40">
+        <v>21.7</v>
+      </c>
+      <c r="F40">
+        <v>-35</v>
+      </c>
       <c r="H40" t="s">
         <v>6</v>
       </c>

--- a/backstage_llm/noblank-newtokenize/test_result.xlsx
+++ b/backstage_llm/noblank-newtokenize/test_result.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="27">
   <si>
     <t>all vs full</t>
   </si>
@@ -77,6 +77,9 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
+    <t>bm80</t>
+  </si>
+  <si>
     <t>high_school_geography</t>
   </si>
   <si>
@@ -86,7 +89,7 @@
     <t>0.6000000000000014</t>
   </si>
   <si>
-    <t>bm80</t>
+    <t>2.5000000000000004</t>
   </si>
   <si>
     <t>college_medicine</t>
@@ -1264,7 +1267,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="29.6153846153846" customWidth="1"/>
@@ -1464,7 +1467,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="2:6">
+    <row r="17" spans="2:8">
       <c r="B17" t="s">
         <v>10</v>
       </c>
@@ -1480,362 +1483,415 @@
       <c r="F17">
         <v>-32.9</v>
       </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" t="s">
+      <c r="H17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" t="s">
         <v>16</v>
       </c>
-      <c r="I19" t="s">
+      <c r="H18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="B19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="3:9">
-      <c r="C20" t="s">
+    <row r="22" spans="3:9">
+      <c r="C22" t="s">
         <v>2</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D22" t="s">
         <v>3</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E22" t="s">
         <v>4</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F22" t="s">
         <v>5</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H22" t="s">
         <v>14</v>
       </c>
-      <c r="I20">
+      <c r="I22">
         <v>22475</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9">
-      <c r="B21" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21">
-        <v>3</v>
-      </c>
-      <c r="D21">
-        <v>8</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F21">
-        <v>-12.7999999999999</v>
-      </c>
-      <c r="H21" t="s">
-        <v>6</v>
-      </c>
-      <c r="I21">
-        <v>21961</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9">
-      <c r="B22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22">
-        <v>3</v>
-      </c>
-      <c r="D22">
-        <v>9</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F22">
-        <v>-20.9999999999999</v>
-      </c>
-      <c r="H22" t="s">
-        <v>10</v>
-      </c>
-      <c r="I22">
-        <v>20804</v>
       </c>
     </row>
     <row r="23" spans="2:9">
       <c r="B23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>3</v>
+      </c>
+      <c r="D23">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23">
+        <v>-12.7999999999999</v>
+      </c>
+      <c r="H23" t="s">
+        <v>6</v>
+      </c>
+      <c r="I23">
+        <v>21961</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9">
+      <c r="B24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24">
+        <v>3</v>
+      </c>
+      <c r="D24">
+        <v>9</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H23" t="s">
+      <c r="F24">
+        <v>-20.9999999999999</v>
+      </c>
+      <c r="H24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I24">
+        <v>20804</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9">
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25">
+        <v>4</v>
+      </c>
+      <c r="D25">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25">
+        <v>-32.5</v>
+      </c>
+      <c r="H25" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25">
+        <v>16174</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8">
+      <c r="B26" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>21</v>
+      </c>
+      <c r="I28" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="3:9">
+      <c r="C29" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" t="s">
+        <v>4</v>
+      </c>
+      <c r="F29" t="s">
+        <v>5</v>
+      </c>
+      <c r="H29" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29">
+        <v>19999</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9">
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30">
+        <v>6</v>
+      </c>
+      <c r="D30">
+        <v>9</v>
+      </c>
+      <c r="E30">
+        <v>11.7</v>
+      </c>
+      <c r="F30">
+        <v>-15.3</v>
+      </c>
+      <c r="H30" t="s">
+        <v>6</v>
+      </c>
+      <c r="I30">
+        <v>14804</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9">
+      <c r="B31" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31">
+        <v>9</v>
+      </c>
+      <c r="D31">
+        <v>7</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31">
+        <v>-21.8</v>
+      </c>
+      <c r="H31" t="s">
+        <v>10</v>
+      </c>
+      <c r="I31">
+        <v>12010</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9">
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32">
+        <v>9</v>
+      </c>
+      <c r="D32">
+        <v>6</v>
+      </c>
+      <c r="E32">
+        <v>21.1</v>
+      </c>
+      <c r="F32">
+        <v>-27.2</v>
+      </c>
+      <c r="H32" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32">
+        <v>8572</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9">
+      <c r="B33" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33" t="s">
+        <v>11</v>
+      </c>
+      <c r="I33">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" t="s">
+        <v>23</v>
+      </c>
+      <c r="I35" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9">
+      <c r="C36" t="s">
+        <v>2</v>
+      </c>
+      <c r="D36" t="s">
+        <v>3</v>
+      </c>
+      <c r="E36" t="s">
+        <v>4</v>
+      </c>
+      <c r="F36" t="s">
+        <v>5</v>
+      </c>
+      <c r="H36" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36">
+        <v>13791</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9">
+      <c r="B37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37">
+        <v>15</v>
+      </c>
+      <c r="D37">
+        <v>16</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F37">
+        <v>-14.7</v>
+      </c>
+      <c r="H37" t="s">
+        <v>6</v>
+      </c>
+      <c r="I37">
+        <v>12996</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9">
+      <c r="B38" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38">
+        <v>15</v>
+      </c>
+      <c r="D38">
         <v>19</v>
       </c>
-      <c r="I23">
-        <v>16174</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" t="s">
-        <v>20</v>
-      </c>
-      <c r="I25" t="s">
+      <c r="E38" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F38">
+        <v>-41.3999999999999</v>
+      </c>
+      <c r="H38" t="s">
+        <v>10</v>
+      </c>
+      <c r="I38">
+        <v>11284</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9">
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="H39" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39">
+        <v>7562</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8">
+      <c r="B40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H40" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" t="s">
+        <v>26</v>
+      </c>
+      <c r="I42" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="3:9">
-      <c r="C26" t="s">
+    <row r="43" spans="3:9">
+      <c r="C43" t="s">
         <v>2</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D43" t="s">
         <v>3</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E43" t="s">
         <v>4</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F43" t="s">
         <v>5</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H43" t="s">
         <v>14</v>
       </c>
-      <c r="I26">
-        <v>19999</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9">
-      <c r="B27" t="s">
+      <c r="I43">
+        <v>34556</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9">
+      <c r="B44" t="s">
         <v>6</v>
       </c>
-      <c r="C27">
+      <c r="C44">
+        <v>8</v>
+      </c>
+      <c r="D44">
+        <v>11</v>
+      </c>
+      <c r="E44">
+        <v>21.7</v>
+      </c>
+      <c r="F44">
+        <v>-35</v>
+      </c>
+      <c r="H44" t="s">
         <v>6</v>
       </c>
-      <c r="D27">
-        <v>9</v>
-      </c>
-      <c r="E27">
-        <v>11.7</v>
-      </c>
-      <c r="F27">
-        <v>-15.3</v>
-      </c>
-      <c r="H27" t="s">
-        <v>6</v>
-      </c>
-      <c r="I27">
-        <v>14804</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9">
-      <c r="B28" t="s">
+      <c r="I44">
+        <v>26342</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9">
+      <c r="B45" t="s">
         <v>10</v>
       </c>
-      <c r="C28">
-        <v>9</v>
-      </c>
-      <c r="D28">
-        <v>7</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28">
-        <v>-21.8</v>
-      </c>
-      <c r="H28" t="s">
+      <c r="C45"/>
+      <c r="D45"/>
+      <c r="E45"/>
+      <c r="F45"/>
+      <c r="H45" t="s">
         <v>10</v>
       </c>
-      <c r="I28">
-        <v>12010</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9">
-      <c r="B29" t="s">
-        <v>19</v>
-      </c>
-      <c r="C29">
-        <v>9</v>
-      </c>
-      <c r="D29">
-        <v>6</v>
-      </c>
-      <c r="E29">
-        <v>21.1</v>
-      </c>
-      <c r="F29">
-        <v>-27.2</v>
-      </c>
-      <c r="H29" t="s">
-        <v>19</v>
-      </c>
-      <c r="I29">
-        <v>8572</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8">
-      <c r="B30" t="s">
+      <c r="I45">
+        <v>18391</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8">
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46"/>
+      <c r="D46"/>
+      <c r="E46"/>
+      <c r="F46"/>
+      <c r="H46" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8">
+      <c r="B47" t="s">
         <v>11</v>
       </c>
-      <c r="H30" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" t="s">
-        <v>22</v>
-      </c>
-      <c r="I32" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9">
-      <c r="C33" t="s">
-        <v>2</v>
-      </c>
-      <c r="D33" t="s">
-        <v>3</v>
-      </c>
-      <c r="E33" t="s">
-        <v>4</v>
-      </c>
-      <c r="F33" t="s">
-        <v>5</v>
-      </c>
-      <c r="H33" t="s">
-        <v>14</v>
-      </c>
-      <c r="I33">
-        <v>13791</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9">
-      <c r="B34" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34">
-        <v>15</v>
-      </c>
-      <c r="D34">
-        <v>16</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F34">
-        <v>-14.7</v>
-      </c>
-      <c r="H34" t="s">
-        <v>6</v>
-      </c>
-      <c r="I34">
-        <v>12996</v>
-      </c>
-    </row>
-    <row r="35" spans="2:9">
-      <c r="B35" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35">
-        <v>15</v>
-      </c>
-      <c r="D35">
-        <v>19</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F35">
-        <v>-41.3999999999999</v>
-      </c>
-      <c r="H35" t="s">
-        <v>10</v>
-      </c>
-      <c r="I35">
-        <v>11284</v>
-      </c>
-    </row>
-    <row r="36" spans="2:9">
-      <c r="B36" t="s">
-        <v>19</v>
-      </c>
-      <c r="H36" t="s">
-        <v>19</v>
-      </c>
-      <c r="I36">
-        <v>7562</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
-      <c r="A38" t="s">
-        <v>25</v>
-      </c>
-      <c r="I38" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" spans="3:9">
-      <c r="C39" t="s">
-        <v>2</v>
-      </c>
-      <c r="D39" t="s">
-        <v>3</v>
-      </c>
-      <c r="E39" t="s">
-        <v>4</v>
-      </c>
-      <c r="F39" t="s">
-        <v>5</v>
-      </c>
-      <c r="H39" t="s">
-        <v>14</v>
-      </c>
-      <c r="I39">
-        <v>34556</v>
-      </c>
-    </row>
-    <row r="40" spans="2:9">
-      <c r="B40" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40">
-        <v>8</v>
-      </c>
-      <c r="D40">
-        <v>11</v>
-      </c>
-      <c r="E40">
-        <v>21.7</v>
-      </c>
-      <c r="F40">
-        <v>-35</v>
-      </c>
-      <c r="H40" t="s">
-        <v>6</v>
-      </c>
-      <c r="I40">
-        <v>26342</v>
-      </c>
-    </row>
-    <row r="41" spans="2:8">
-      <c r="B41" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41"/>
-      <c r="D41"/>
-      <c r="E41"/>
-      <c r="F41"/>
-      <c r="H41" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42" spans="2:8">
-      <c r="B42" t="s">
-        <v>19</v>
-      </c>
-      <c r="C42"/>
-      <c r="D42"/>
-      <c r="E42"/>
-      <c r="F42"/>
-      <c r="H42" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="43" spans="2:8">
-      <c r="B43" t="s">
-        <v>11</v>
-      </c>
-      <c r="H43" t="s">
+      <c r="H47" t="s">
         <v>11</v>
       </c>
     </row>

--- a/backstage_llm/noblank-newtokenize/test_result.xlsx
+++ b/backstage_llm/noblank-newtokenize/test_result.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28760" windowHeight="15300"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -115,10 +115,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -584,19 +584,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1268,12 +1268,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I47"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.22727272727273" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="29.6153846153846" customWidth="1"/>
-    <col min="3" max="3" width="11.0769230769231" customWidth="1"/>
-    <col min="4" max="4" width="13.2307692307692" customWidth="1"/>
-    <col min="5" max="5" width="20.2307692307692" customWidth="1"/>
+    <col min="1" max="1" width="29.6181818181818" customWidth="1"/>
+    <col min="3" max="3" width="11.0727272727273" customWidth="1"/>
+    <col min="4" max="4" width="13.2272727272727" customWidth="1"/>
+    <col min="5" max="5" width="20.2272727272727" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1600,12 +1600,15 @@
         <v>16174</v>
       </c>
     </row>
-    <row r="26" spans="2:8">
+    <row r="26" spans="2:9">
       <c r="B26" t="s">
         <v>11</v>
       </c>
       <c r="H26" t="s">
         <v>11</v>
+      </c>
+      <c r="I26">
+        <v>1170</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1864,10 +1867,6 @@
       <c r="B45" t="s">
         <v>10</v>
       </c>
-      <c r="C45"/>
-      <c r="D45"/>
-      <c r="E45"/>
-      <c r="F45"/>
       <c r="H45" t="s">
         <v>10</v>
       </c>
@@ -1879,10 +1878,6 @@
       <c r="B46" t="s">
         <v>16</v>
       </c>
-      <c r="C46"/>
-      <c r="D46"/>
-      <c r="E46"/>
-      <c r="F46"/>
       <c r="H46" t="s">
         <v>16</v>
       </c>

--- a/backstage_llm/noblank-newtokenize/test_result.xlsx
+++ b/backstage_llm/noblank-newtokenize/test_result.xlsx
@@ -27,29 +27,89 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="30">
+  <si>
+    <t>problem set size</t>
+  </si>
+  <si>
+    <t>condensed size</t>
+  </si>
   <si>
     <t>all vs full</t>
   </si>
   <si>
+    <t>college_biology</t>
+  </si>
+  <si>
+    <t>size</t>
+  </si>
+  <si>
+    <t>full</t>
+  </si>
+  <si>
+    <t>full_better</t>
+  </si>
+  <si>
+    <t>distill_better</t>
+  </si>
+  <si>
+    <t>full_accumulate</t>
+  </si>
+  <si>
+    <t>distill_accumulate</t>
+  </si>
+  <si>
+    <t>bm120</t>
+  </si>
+  <si>
+    <t>bm100</t>
+  </si>
+  <si>
+    <t>bm80</t>
+  </si>
+  <si>
+    <t>bm40</t>
+  </si>
+  <si>
+    <t>high_school_geography</t>
+  </si>
+  <si>
+    <t>0.7000000000000011</t>
+  </si>
+  <si>
+    <t>0.6000000000000014</t>
+  </si>
+  <si>
+    <t>2.5000000000000004</t>
+  </si>
+  <si>
+    <t>college_medicine</t>
+  </si>
+  <si>
+    <t>17.999999999999996</t>
+  </si>
+  <si>
+    <t>90.80000000000001</t>
+  </si>
+  <si>
+    <t>international_law</t>
+  </si>
+  <si>
+    <t>10.999999999999996</t>
+  </si>
+  <si>
+    <t>18.799999999999997</t>
+  </si>
+  <si>
+    <t>45.89999999999999</t>
+  </si>
+  <si>
+    <t>high_school_biology</t>
+  </si>
+  <si>
     <t>high_school_biology first 100</t>
   </si>
   <si>
-    <t>full_better</t>
-  </si>
-  <si>
-    <t>distill_better</t>
-  </si>
-  <si>
-    <t>full_accumulate</t>
-  </si>
-  <si>
-    <t>distill_accumulate</t>
-  </si>
-  <si>
-    <t>bm120</t>
-  </si>
-  <si>
     <t>bm100_0</t>
   </si>
   <si>
@@ -57,57 +117,6 @@
   </si>
   <si>
     <t>high_school_geography first 100</t>
-  </si>
-  <si>
-    <t>bm100</t>
-  </si>
-  <si>
-    <t>bm40</t>
-  </si>
-  <si>
-    <t>college_biology</t>
-  </si>
-  <si>
-    <t>size</t>
-  </si>
-  <si>
-    <t>full</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>bm80</t>
-  </si>
-  <si>
-    <t>high_school_geography</t>
-  </si>
-  <si>
-    <t>0.7000000000000011</t>
-  </si>
-  <si>
-    <t>0.6000000000000014</t>
-  </si>
-  <si>
-    <t>2.5000000000000004</t>
-  </si>
-  <si>
-    <t>college_medicine</t>
-  </si>
-  <si>
-    <t>17.999999999999996</t>
-  </si>
-  <si>
-    <t>international_law</t>
-  </si>
-  <si>
-    <t>10.999999999999996</t>
-  </si>
-  <si>
-    <t>18.799999999999997</t>
-  </si>
-  <si>
-    <t>high_school_biology</t>
   </si>
 </sst>
 </file>
@@ -120,19 +129,13 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9.75"/>
-      <color theme="1"/>
-      <name val="Menlo"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -279,12 +282,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -599,70 +614,64 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -671,10 +680,10 @@
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,10 +692,10 @@
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,10 +704,10 @@
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -707,10 +716,10 @@
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -719,28 +728,37 @@
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" quotePrefix="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1267,627 +1285,699 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr defaultColWidth="9.22727272727273" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="29.6181818181818" customWidth="1"/>
-    <col min="3" max="3" width="11.0727272727273" customWidth="1"/>
-    <col min="4" max="4" width="13.2272727272727" customWidth="1"/>
-    <col min="5" max="5" width="20.2272727272727" customWidth="1"/>
-    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="1" max="1" width="35.3636363636364" customWidth="1"/>
+    <col min="8" max="8" width="11.0727272727273" customWidth="1"/>
+    <col min="9" max="9" width="13.2272727272727" customWidth="1"/>
+    <col min="10" max="10" width="20.2272727272727" customWidth="1"/>
+    <col min="11" max="11" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="8:8">
-      <c r="H1" t="s">
+    <row r="1" spans="2:7">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="3:6">
-      <c r="C3" t="s">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11">
+      <c r="B3">
+        <v>165</v>
       </c>
       <c r="D3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="2:6">
-      <c r="B4" t="s">
+      <c r="E3">
+        <v>16493</v>
+      </c>
+      <c r="H3" t="s">
         <v>6</v>
       </c>
-      <c r="C4">
+      <c r="I3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" t="s">
         <v>9</v>
       </c>
-      <c r="D4">
-        <v>8</v>
+    </row>
+    <row r="4" spans="4:11">
+      <c r="D4" t="s">
+        <v>10</v>
       </c>
       <c r="E4">
-        <v>14.1</v>
-      </c>
-      <c r="F4">
-        <v>-30.7999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6">
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5">
+        <v>14112</v>
+      </c>
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4">
+        <v>11</v>
+      </c>
+      <c r="I4">
+        <v>11</v>
+      </c>
+      <c r="J4" s="1">
+        <v>34.2</v>
+      </c>
+      <c r="K4" s="1">
+        <v>-20.5</v>
+      </c>
+    </row>
+    <row r="5" spans="4:11">
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5">
+        <v>12015</v>
+      </c>
+      <c r="G5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5">
+        <v>14</v>
+      </c>
+      <c r="I5">
+        <v>12</v>
+      </c>
+      <c r="J5" s="1">
+        <v>36.9</v>
+      </c>
+      <c r="K5" s="1">
+        <v>-32.9</v>
+      </c>
+    </row>
+    <row r="6" spans="4:7">
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6">
+        <v>7435</v>
+      </c>
+      <c r="G6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="4:7">
+      <c r="D7" t="s">
         <v>13</v>
       </c>
-      <c r="D5">
-        <v>10</v>
-      </c>
-      <c r="E5">
-        <v>21.0999999999999</v>
-      </c>
-      <c r="F5">
-        <v>-32.2</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6">
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>16</v>
-      </c>
-      <c r="D6">
-        <v>8</v>
-      </c>
-      <c r="E6">
-        <v>21.5999999999999</v>
-      </c>
-      <c r="F6">
-        <v>-29.2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="3:6">
-      <c r="C9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" t="s">
-        <v>3</v>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>14</v>
       </c>
       <c r="E9" t="s">
         <v>4</v>
       </c>
-      <c r="F9" t="s">
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10">
+        <v>225</v>
+      </c>
+      <c r="D10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="2:6">
-      <c r="B10" t="s">
+      <c r="E10">
+        <v>22475</v>
+      </c>
+      <c r="H10" t="s">
         <v>6</v>
       </c>
-      <c r="C10">
+      <c r="I10" t="s">
+        <v>7</v>
+      </c>
+      <c r="J10" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="4:11">
+      <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11">
+        <v>21961</v>
+      </c>
+      <c r="G11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11">
+        <v>3</v>
+      </c>
+      <c r="I11">
+        <v>8</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K11" s="2">
+        <v>-12.7999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="4:11">
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12">
+        <v>20804</v>
+      </c>
+      <c r="G12" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12">
+        <v>3</v>
+      </c>
+      <c r="I12">
+        <v>9</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="2">
+        <v>-20.9999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="4:11">
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13">
+        <v>16174</v>
+      </c>
+      <c r="G13" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13">
         <v>4</v>
       </c>
-      <c r="D10">
+      <c r="I13">
+        <v>8</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K13" s="2">
+        <v>-32.5</v>
+      </c>
+    </row>
+    <row r="14" spans="4:7">
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14">
+        <v>1170</v>
+      </c>
+      <c r="G14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17">
+        <v>200</v>
+      </c>
+      <c r="D17" t="s">
         <v>5</v>
       </c>
-      <c r="E10">
-        <v>2.09999999999999</v>
-      </c>
-      <c r="F10">
-        <v>-3.29999999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6">
-      <c r="B11" t="s">
+      <c r="E17">
+        <v>19999</v>
+      </c>
+      <c r="H17" t="s">
+        <v>6</v>
+      </c>
+      <c r="I17" t="s">
+        <v>7</v>
+      </c>
+      <c r="J17" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="4:11">
+      <c r="D18" t="s">
         <v>10</v>
       </c>
-      <c r="C11">
-        <v>3</v>
-      </c>
-      <c r="D11">
+      <c r="E18">
+        <v>14804</v>
+      </c>
+      <c r="G18" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18">
+        <v>6</v>
+      </c>
+      <c r="I18">
+        <v>9</v>
+      </c>
+      <c r="J18" s="2">
+        <v>11.7</v>
+      </c>
+      <c r="K18" s="2">
+        <v>-15.3</v>
+      </c>
+    </row>
+    <row r="19" spans="4:11">
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19">
+        <v>12010</v>
+      </c>
+      <c r="G19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H19">
+        <v>9</v>
+      </c>
+      <c r="I19">
+        <v>7</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K19" s="2">
+        <v>-21.8</v>
+      </c>
+    </row>
+    <row r="20" spans="4:11">
+      <c r="D20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20">
+        <v>8572</v>
+      </c>
+      <c r="G20" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20">
+        <v>9</v>
+      </c>
+      <c r="I20">
+        <v>6</v>
+      </c>
+      <c r="J20" s="2">
+        <v>21.1</v>
+      </c>
+      <c r="K20" s="2">
+        <v>-27.2</v>
+      </c>
+    </row>
+    <row r="21" spans="4:11">
+      <c r="D21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21">
+        <v>719</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21">
+        <v>20</v>
+      </c>
+      <c r="I21">
+        <v>7</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K21" s="1">
+        <v>-34.4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24">
+        <v>139</v>
+      </c>
+      <c r="D24" t="s">
         <v>5</v>
       </c>
-      <c r="E11">
-        <v>1.59999999999999</v>
-      </c>
-      <c r="F11">
-        <v>-3.79999999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6">
-      <c r="B12" t="s">
+      <c r="E24">
+        <v>13791</v>
+      </c>
+      <c r="H24" t="s">
+        <v>6</v>
+      </c>
+      <c r="I24" t="s">
+        <v>7</v>
+      </c>
+      <c r="J24" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="4:11">
+      <c r="D25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25">
+        <v>12996</v>
+      </c>
+      <c r="G25" t="s">
+        <v>10</v>
+      </c>
+      <c r="H25">
+        <v>15</v>
+      </c>
+      <c r="I25">
+        <v>16</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K25" s="2">
+        <v>-14.7</v>
+      </c>
+    </row>
+    <row r="26" spans="4:11">
+      <c r="D26" t="s">
         <v>11</v>
       </c>
-      <c r="C12">
+      <c r="E26">
+        <v>11284</v>
+      </c>
+      <c r="G26" t="s">
         <v>11</v>
       </c>
-      <c r="D12">
+      <c r="H26">
+        <v>15</v>
+      </c>
+      <c r="I26">
+        <v>19</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K26" s="2">
+        <v>-41.3999999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="4:11">
+      <c r="D27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27">
+        <v>7562</v>
+      </c>
+      <c r="G27" t="s">
+        <v>12</v>
+      </c>
+      <c r="H27">
+        <v>20</v>
+      </c>
+      <c r="I27">
+        <v>18</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K27" s="1">
+        <v>-34.7999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="4:7">
+      <c r="D28" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28">
+        <v>700</v>
+      </c>
+      <c r="G28" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31">
+        <v>347</v>
+      </c>
+      <c r="D31" t="s">
+        <v>5</v>
+      </c>
+      <c r="E31">
+        <v>34556</v>
+      </c>
+      <c r="H31" t="s">
+        <v>6</v>
+      </c>
+      <c r="I31" t="s">
+        <v>7</v>
+      </c>
+      <c r="J31" t="s">
+        <v>8</v>
+      </c>
+      <c r="K31" t="s">
         <v>9</v>
       </c>
-      <c r="E12">
-        <v>50.8</v>
-      </c>
-      <c r="F12">
-        <v>-28.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" t="s">
+    </row>
+    <row r="32" spans="4:11">
+      <c r="D32" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32">
+        <v>26342</v>
+      </c>
+      <c r="G32" t="s">
+        <v>10</v>
+      </c>
+      <c r="H32">
+        <v>8</v>
+      </c>
+      <c r="I32">
+        <v>11</v>
+      </c>
+      <c r="J32" s="2">
+        <v>21.7</v>
+      </c>
+      <c r="K32" s="2">
+        <v>-35</v>
+      </c>
+    </row>
+    <row r="33" spans="4:7">
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33">
+        <v>18391</v>
+      </c>
+      <c r="G33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="4:7">
+      <c r="D34" t="s">
         <v>12</v>
       </c>
-      <c r="I14" t="s">
+      <c r="G34" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="4:7">
+      <c r="D35" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="3:8">
-      <c r="C15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" t="s">
-        <v>5</v>
-      </c>
-      <c r="H15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8">
-      <c r="B16" t="s">
+      <c r="G35" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="8:11">
+      <c r="H38" t="s">
         <v>6</v>
       </c>
-      <c r="C16">
-        <v>11</v>
-      </c>
-      <c r="D16" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16">
-        <v>34.2</v>
-      </c>
-      <c r="F16">
-        <v>-20.5</v>
-      </c>
-      <c r="H16" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8">
-      <c r="B17" t="s">
+      <c r="I38" t="s">
+        <v>7</v>
+      </c>
+      <c r="J38" t="s">
+        <v>8</v>
+      </c>
+      <c r="K38" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="7:11">
+      <c r="G39" t="s">
         <v>10</v>
       </c>
-      <c r="C17">
-        <v>14</v>
-      </c>
-      <c r="D17">
-        <v>12</v>
-      </c>
-      <c r="E17">
-        <v>36.9</v>
-      </c>
-      <c r="F17">
-        <v>-32.9</v>
-      </c>
-      <c r="H17" t="s">
+      <c r="H39">
+        <v>9</v>
+      </c>
+      <c r="I39">
+        <v>8</v>
+      </c>
+      <c r="J39" s="2">
+        <v>14.1</v>
+      </c>
+      <c r="K39" s="2">
+        <v>-30.7999999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="7:11">
+      <c r="G40" t="s">
+        <v>27</v>
+      </c>
+      <c r="H40">
+        <v>13</v>
+      </c>
+      <c r="I40">
         <v>10</v>
       </c>
-    </row>
-    <row r="18" spans="2:8">
-      <c r="B18" t="s">
+      <c r="J40" s="2">
+        <v>21.0999999999999</v>
+      </c>
+      <c r="K40" s="2">
+        <v>-32.2</v>
+      </c>
+    </row>
+    <row r="41" spans="7:11">
+      <c r="G41" t="s">
+        <v>28</v>
+      </c>
+      <c r="H41">
         <v>16</v>
       </c>
-      <c r="H18" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8">
-      <c r="B19" t="s">
-        <v>11</v>
-      </c>
-      <c r="H19" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" t="s">
-        <v>17</v>
-      </c>
-      <c r="I21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="3:9">
-      <c r="C22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D22" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" t="s">
-        <v>5</v>
-      </c>
-      <c r="H22" t="s">
-        <v>14</v>
-      </c>
-      <c r="I22">
-        <v>22475</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9">
-      <c r="B23" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23">
-        <v>3</v>
-      </c>
-      <c r="D23">
+      <c r="I41">
         <v>8</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F23">
-        <v>-12.7999999999999</v>
-      </c>
-      <c r="H23" t="s">
-        <v>6</v>
-      </c>
-      <c r="I23">
-        <v>21961</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9">
-      <c r="B24" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24">
-        <v>3</v>
-      </c>
-      <c r="D24">
-        <v>9</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F24">
-        <v>-20.9999999999999</v>
-      </c>
-      <c r="H24" t="s">
-        <v>10</v>
-      </c>
-      <c r="I24">
-        <v>20804</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9">
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25">
-        <v>4</v>
-      </c>
-      <c r="D25">
-        <v>8</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F25">
-        <v>-32.5</v>
-      </c>
-      <c r="H25" t="s">
-        <v>16</v>
-      </c>
-      <c r="I25">
-        <v>16174</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9">
-      <c r="B26" t="s">
-        <v>11</v>
-      </c>
-      <c r="H26" t="s">
-        <v>11</v>
-      </c>
-      <c r="I26">
-        <v>1170</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" t="s">
-        <v>21</v>
-      </c>
-      <c r="I28" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="3:9">
-      <c r="C29" t="s">
-        <v>2</v>
-      </c>
-      <c r="D29" t="s">
-        <v>3</v>
-      </c>
-      <c r="E29" t="s">
-        <v>4</v>
-      </c>
-      <c r="F29" t="s">
-        <v>5</v>
-      </c>
-      <c r="H29" t="s">
-        <v>14</v>
-      </c>
-      <c r="I29">
-        <v>19999</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9">
-      <c r="B30" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30">
-        <v>6</v>
-      </c>
-      <c r="D30">
-        <v>9</v>
-      </c>
-      <c r="E30">
-        <v>11.7</v>
-      </c>
-      <c r="F30">
-        <v>-15.3</v>
-      </c>
-      <c r="H30" t="s">
-        <v>6</v>
-      </c>
-      <c r="I30">
-        <v>14804</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9">
-      <c r="B31" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31">
-        <v>9</v>
-      </c>
-      <c r="D31">
-        <v>7</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F31">
-        <v>-21.8</v>
-      </c>
-      <c r="H31" t="s">
-        <v>10</v>
-      </c>
-      <c r="I31">
-        <v>12010</v>
-      </c>
-    </row>
-    <row r="32" spans="2:9">
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32">
-        <v>9</v>
-      </c>
-      <c r="D32">
-        <v>6</v>
-      </c>
-      <c r="E32">
-        <v>21.1</v>
-      </c>
-      <c r="F32">
-        <v>-27.2</v>
-      </c>
-      <c r="H32" t="s">
-        <v>16</v>
-      </c>
-      <c r="I32">
-        <v>8572</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9">
-      <c r="B33" t="s">
-        <v>11</v>
-      </c>
-      <c r="H33" t="s">
-        <v>11</v>
-      </c>
-      <c r="I33">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
-      <c r="A35" t="s">
-        <v>23</v>
-      </c>
-      <c r="I35" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" spans="3:9">
-      <c r="C36" t="s">
-        <v>2</v>
-      </c>
-      <c r="D36" t="s">
-        <v>3</v>
-      </c>
-      <c r="E36" t="s">
-        <v>4</v>
-      </c>
-      <c r="F36" t="s">
-        <v>5</v>
-      </c>
-      <c r="H36" t="s">
-        <v>14</v>
-      </c>
-      <c r="I36">
-        <v>13791</v>
-      </c>
-    </row>
-    <row r="37" spans="2:9">
-      <c r="B37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37">
-        <v>15</v>
-      </c>
-      <c r="D37">
-        <v>16</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F37">
-        <v>-14.7</v>
-      </c>
-      <c r="H37" t="s">
-        <v>6</v>
-      </c>
-      <c r="I37">
-        <v>12996</v>
-      </c>
-    </row>
-    <row r="38" spans="2:9">
-      <c r="B38" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38">
-        <v>15</v>
-      </c>
-      <c r="D38">
-        <v>19</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F38">
-        <v>-41.3999999999999</v>
-      </c>
-      <c r="H38" t="s">
-        <v>10</v>
-      </c>
-      <c r="I38">
-        <v>11284</v>
-      </c>
-    </row>
-    <row r="39" spans="2:9">
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="H39" t="s">
-        <v>16</v>
-      </c>
-      <c r="I39">
-        <v>7562</v>
-      </c>
-    </row>
-    <row r="40" spans="2:8">
-      <c r="B40" t="s">
-        <v>11</v>
-      </c>
-      <c r="H40" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9">
-      <c r="A42" t="s">
-        <v>26</v>
-      </c>
-      <c r="I42" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43" spans="3:9">
-      <c r="C43" t="s">
-        <v>2</v>
-      </c>
-      <c r="D43" t="s">
-        <v>3</v>
-      </c>
-      <c r="E43" t="s">
-        <v>4</v>
-      </c>
-      <c r="F43" t="s">
-        <v>5</v>
-      </c>
-      <c r="H43" t="s">
-        <v>14</v>
-      </c>
-      <c r="I43">
-        <v>34556</v>
-      </c>
-    </row>
-    <row r="44" spans="2:9">
-      <c r="B44" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44">
-        <v>8</v>
-      </c>
-      <c r="D44">
-        <v>11</v>
-      </c>
-      <c r="E44">
-        <v>21.7</v>
-      </c>
-      <c r="F44">
-        <v>-35</v>
-      </c>
+      <c r="J41" s="2">
+        <v>21.5999999999999</v>
+      </c>
+      <c r="K41" s="2">
+        <v>-29.2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="44" spans="8:11">
       <c r="H44" t="s">
         <v>6</v>
       </c>
-      <c r="I44">
-        <v>26342</v>
-      </c>
-    </row>
-    <row r="45" spans="2:9">
-      <c r="B45" t="s">
+      <c r="I44" t="s">
+        <v>7</v>
+      </c>
+      <c r="J44" t="s">
+        <v>8</v>
+      </c>
+      <c r="K44" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="7:11">
+      <c r="G45" t="s">
         <v>10</v>
       </c>
-      <c r="H45" t="s">
-        <v>10</v>
+      <c r="H45">
+        <v>4</v>
       </c>
       <c r="I45">
-        <v>18391</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8">
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="H46" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8">
-      <c r="B47" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="2">
+        <v>2.09999999999999</v>
+      </c>
+      <c r="K45" s="2">
+        <v>-3.29999999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="7:11">
+      <c r="G46" t="s">
         <v>11</v>
       </c>
-      <c r="H47" t="s">
+      <c r="H46">
+        <v>3</v>
+      </c>
+      <c r="I46">
+        <v>5</v>
+      </c>
+      <c r="J46" s="2">
+        <v>1.59999999999999</v>
+      </c>
+      <c r="K46" s="2">
+        <v>-3.79999999999999</v>
+      </c>
+    </row>
+    <row r="47" spans="7:11">
+      <c r="G47" t="s">
+        <v>13</v>
+      </c>
+      <c r="H47">
         <v>11</v>
+      </c>
+      <c r="I47">
+        <v>9</v>
+      </c>
+      <c r="J47" s="2">
+        <v>50.8</v>
+      </c>
+      <c r="K47" s="2">
+        <v>-28.5</v>
       </c>
     </row>
   </sheetData>

--- a/backstage_llm/noblank-newtokenize/test_result.xlsx
+++ b/backstage_llm/noblank-newtokenize/test_result.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="31">
   <si>
     <t>problem set size</t>
   </si>
@@ -38,37 +38,49 @@
     <t>all vs full</t>
   </si>
   <si>
+    <t>college_medicine</t>
+  </si>
+  <si>
+    <t>size</t>
+  </si>
+  <si>
+    <t>full</t>
+  </si>
+  <si>
+    <t>full_better</t>
+  </si>
+  <si>
+    <t>distill_better</t>
+  </si>
+  <si>
+    <t>full_accumulate</t>
+  </si>
+  <si>
+    <t>distill_accumulate</t>
+  </si>
+  <si>
+    <t>bm120</t>
+  </si>
+  <si>
+    <t>bm100</t>
+  </si>
+  <si>
+    <t>17.999999999999996</t>
+  </si>
+  <si>
+    <t>bm80</t>
+  </si>
+  <si>
+    <t>bm40</t>
+  </si>
+  <si>
+    <t>90.80000000000001</t>
+  </si>
+  <si>
     <t>college_biology</t>
   </si>
   <si>
-    <t>size</t>
-  </si>
-  <si>
-    <t>full</t>
-  </si>
-  <si>
-    <t>full_better</t>
-  </si>
-  <si>
-    <t>distill_better</t>
-  </si>
-  <si>
-    <t>full_accumulate</t>
-  </si>
-  <si>
-    <t>distill_accumulate</t>
-  </si>
-  <si>
-    <t>bm120</t>
-  </si>
-  <si>
-    <t>bm100</t>
-  </si>
-  <si>
-    <t>bm80</t>
-  </si>
-  <si>
-    <t>bm40</t>
+    <t>45.49999999999999</t>
   </si>
   <si>
     <t>high_school_geography</t>
@@ -81,15 +93,6 @@
   </si>
   <si>
     <t>2.5000000000000004</t>
-  </si>
-  <si>
-    <t>college_medicine</t>
-  </si>
-  <si>
-    <t>17.999999999999996</t>
-  </si>
-  <si>
-    <t>90.80000000000001</t>
   </si>
   <si>
     <t>international_law</t>
@@ -291,13 +294,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="-0.25"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -754,10 +757,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" quotePrefix="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1316,13 +1319,13 @@
     </row>
     <row r="3" spans="2:11">
       <c r="B3">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
       </c>
       <c r="E3">
-        <v>16493</v>
+        <v>19999</v>
       </c>
       <c r="H3" t="s">
         <v>6</v>
@@ -1342,22 +1345,22 @@
         <v>10</v>
       </c>
       <c r="E4">
-        <v>14112</v>
+        <v>14804</v>
       </c>
       <c r="G4" t="s">
         <v>10</v>
       </c>
       <c r="H4">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J4" s="1">
-        <v>34.2</v>
+        <v>11.7</v>
       </c>
       <c r="K4" s="1">
-        <v>-20.5</v>
+        <v>-15.3</v>
       </c>
     </row>
     <row r="5" spans="4:11">
@@ -1365,63 +1368,87 @@
         <v>11</v>
       </c>
       <c r="E5">
-        <v>12015</v>
+        <v>12010</v>
       </c>
       <c r="G5" t="s">
         <v>11</v>
       </c>
       <c r="H5">
+        <v>9</v>
+      </c>
+      <c r="I5">
+        <v>7</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="1">
+        <v>-21.8</v>
+      </c>
+    </row>
+    <row r="6" spans="4:11">
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6">
+        <v>8572</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6">
+        <v>9</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6" s="1">
+        <v>21.1</v>
+      </c>
+      <c r="K6" s="1">
+        <v>-27.2</v>
+      </c>
+    </row>
+    <row r="7" spans="4:11">
+      <c r="D7" t="s">
         <v>14</v>
       </c>
-      <c r="I5">
-        <v>12</v>
-      </c>
-      <c r="J5" s="1">
-        <v>36.9</v>
-      </c>
-      <c r="K5" s="1">
-        <v>-32.9</v>
-      </c>
-    </row>
-    <row r="6" spans="4:7">
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6">
-        <v>7435</v>
-      </c>
-      <c r="G6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="4:7">
-      <c r="D7" t="s">
-        <v>13</v>
+      <c r="E7">
+        <v>719</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="H7">
+        <v>20</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K7" s="2">
+        <v>-34.4</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
-      <c r="A10" t="s">
-        <v>0</v>
-      </c>
+    <row r="10" spans="2:11">
       <c r="B10">
-        <v>225</v>
+        <v>165</v>
       </c>
       <c r="D10" t="s">
         <v>5</v>
       </c>
       <c r="E10">
-        <v>22475</v>
+        <v>16493</v>
       </c>
       <c r="H10" t="s">
         <v>6</v>
@@ -1441,22 +1468,22 @@
         <v>10</v>
       </c>
       <c r="E11">
-        <v>21961</v>
+        <v>14112</v>
       </c>
       <c r="G11" t="s">
         <v>10</v>
       </c>
       <c r="H11">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I11">
-        <v>8</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
+      </c>
+      <c r="J11" s="2">
+        <v>34.2</v>
       </c>
       <c r="K11" s="2">
-        <v>-12.7999999999999</v>
+        <v>-20.5</v>
       </c>
     </row>
     <row r="12" spans="4:11">
@@ -1464,58 +1491,71 @@
         <v>11</v>
       </c>
       <c r="E12">
-        <v>20804</v>
+        <v>12015</v>
       </c>
       <c r="G12" t="s">
         <v>11</v>
       </c>
       <c r="H12">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I12">
-        <v>9</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
+      </c>
+      <c r="J12" s="2">
+        <v>36.9</v>
       </c>
       <c r="K12" s="2">
-        <v>-20.9999999999999</v>
+        <v>-32.9</v>
       </c>
     </row>
     <row r="13" spans="4:11">
       <c r="D13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E13">
-        <v>16174</v>
+        <v>7435</v>
       </c>
       <c r="G13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H13">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I13">
-        <v>8</v>
-      </c>
-      <c r="J13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J13" s="4" t="s">
         <v>17</v>
       </c>
       <c r="K13" s="2">
-        <v>-32.5</v>
-      </c>
-    </row>
-    <row r="14" spans="4:7">
+        <v>-20.9999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="4:11">
       <c r="D14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E14">
-        <v>1170</v>
+        <v>679</v>
       </c>
       <c r="G14" t="s">
-        <v>13</v>
-      </c>
-    </row>
+        <v>14</v>
+      </c>
+      <c r="H14">
+        <v>19</v>
+      </c>
+      <c r="I14">
+        <v>14</v>
+      </c>
+      <c r="J14" s="2">
+        <v>78.8</v>
+      </c>
+      <c r="K14" s="2">
+        <v>-49.4</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1"/>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>18</v>
@@ -1524,18 +1564,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
-        <v>0</v>
-      </c>
+    <row r="17" spans="2:11">
       <c r="B17">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="D17" t="s">
         <v>5</v>
       </c>
       <c r="E17">
-        <v>19999</v>
+        <v>22475</v>
       </c>
       <c r="H17" t="s">
         <v>6</v>
@@ -1555,22 +1592,22 @@
         <v>10</v>
       </c>
       <c r="E18">
-        <v>14804</v>
+        <v>21961</v>
       </c>
       <c r="G18" t="s">
         <v>10</v>
       </c>
       <c r="H18">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I18">
-        <v>9</v>
-      </c>
-      <c r="J18" s="2">
-        <v>11.7</v>
-      </c>
-      <c r="K18" s="2">
-        <v>-15.3</v>
+        <v>8</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K18" s="1">
+        <v>-12.7999999999999</v>
       </c>
     </row>
     <row r="19" spans="4:11">
@@ -1578,82 +1615,79 @@
         <v>11</v>
       </c>
       <c r="E19">
-        <v>12010</v>
+        <v>20804</v>
       </c>
       <c r="G19" t="s">
         <v>11</v>
       </c>
       <c r="H19">
+        <v>3</v>
+      </c>
+      <c r="I19">
         <v>9</v>
       </c>
-      <c r="I19">
-        <v>7</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K19" s="2">
-        <v>-21.8</v>
+        <v>20</v>
+      </c>
+      <c r="K19" s="1">
+        <v>-20.9999999999999</v>
       </c>
     </row>
     <row r="20" spans="4:11">
       <c r="D20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E20">
-        <v>8572</v>
+        <v>16174</v>
       </c>
       <c r="G20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H20">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I20">
-        <v>6</v>
-      </c>
-      <c r="J20" s="2">
-        <v>21.1</v>
-      </c>
-      <c r="K20" s="2">
-        <v>-27.2</v>
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20" s="1">
+        <v>-32.5</v>
       </c>
     </row>
     <row r="21" spans="4:11">
       <c r="D21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E21">
-        <v>719</v>
+        <v>1170</v>
       </c>
       <c r="G21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H21">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="I21">
-        <v>7</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K21" s="1">
-        <v>-34.4</v>
+        <v>11</v>
+      </c>
+      <c r="J21" s="2">
+        <v>38.4</v>
+      </c>
+      <c r="K21" s="2">
+        <v>-29.7</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E23" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
-      <c r="A24" t="s">
-        <v>0</v>
-      </c>
+    <row r="24" spans="2:11">
       <c r="B24">
         <v>139</v>
       </c>
@@ -1693,9 +1727,9 @@
         <v>16</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K25" s="2">
+        <v>23</v>
+      </c>
+      <c r="K25" s="1">
         <v>-14.7</v>
       </c>
     </row>
@@ -1716,21 +1750,21 @@
         <v>19</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="K26" s="2">
+        <v>24</v>
+      </c>
+      <c r="K26" s="1">
         <v>-41.3999999999999</v>
       </c>
     </row>
     <row r="27" spans="4:11">
       <c r="D27" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E27">
         <v>7562</v>
       </c>
       <c r="G27" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H27">
         <v>20</v>
@@ -1739,35 +1773,32 @@
         <v>18</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="K27" s="1">
+        <v>25</v>
+      </c>
+      <c r="K27" s="2">
         <v>-34.7999999999999</v>
       </c>
     </row>
     <row r="28" spans="4:7">
       <c r="D28" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E28">
         <v>700</v>
       </c>
       <c r="G28" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E30" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
-      <c r="A31" t="s">
-        <v>0</v>
-      </c>
+    <row r="31" spans="2:11">
       <c r="B31">
         <v>347</v>
       </c>
@@ -1806,14 +1837,14 @@
       <c r="I32">
         <v>11</v>
       </c>
-      <c r="J32" s="2">
+      <c r="J32" s="1">
         <v>21.7</v>
       </c>
-      <c r="K32" s="2">
+      <c r="K32" s="1">
         <v>-35</v>
       </c>
     </row>
-    <row r="33" spans="4:7">
+    <row r="33" spans="4:11">
       <c r="D33" t="s">
         <v>11</v>
       </c>
@@ -1823,26 +1854,44 @@
       <c r="G33" t="s">
         <v>11</v>
       </c>
+      <c r="H33">
+        <v>9</v>
+      </c>
+      <c r="I33">
+        <v>12</v>
+      </c>
+      <c r="J33" s="1">
+        <v>29.1</v>
+      </c>
+      <c r="K33" s="1">
+        <v>-44.9999999999999</v>
+      </c>
     </row>
     <row r="34" spans="4:7">
       <c r="D34" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="E34">
+        <v>9974</v>
       </c>
       <c r="G34" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="4:7">
       <c r="D35" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="E35">
+        <v>715</v>
       </c>
       <c r="G35" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="8:11">
@@ -1869,16 +1918,16 @@
       <c r="I39">
         <v>8</v>
       </c>
-      <c r="J39" s="2">
+      <c r="J39" s="1">
         <v>14.1</v>
       </c>
-      <c r="K39" s="2">
+      <c r="K39" s="1">
         <v>-30.7999999999999</v>
       </c>
     </row>
     <row r="40" spans="7:11">
       <c r="G40" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H40">
         <v>13</v>
@@ -1886,16 +1935,16 @@
       <c r="I40">
         <v>10</v>
       </c>
-      <c r="J40" s="2">
+      <c r="J40" s="1">
         <v>21.0999999999999</v>
       </c>
-      <c r="K40" s="2">
+      <c r="K40" s="1">
         <v>-32.2</v>
       </c>
     </row>
     <row r="41" spans="7:11">
       <c r="G41" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H41">
         <v>16</v>
@@ -1903,16 +1952,16 @@
       <c r="I41">
         <v>8</v>
       </c>
-      <c r="J41" s="2">
+      <c r="J41" s="1">
         <v>21.5999999999999</v>
       </c>
-      <c r="K41" s="2">
+      <c r="K41" s="1">
         <v>-29.2</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44" spans="8:11">
@@ -1939,10 +1988,10 @@
       <c r="I45">
         <v>5</v>
       </c>
-      <c r="J45" s="2">
+      <c r="J45" s="1">
         <v>2.09999999999999</v>
       </c>
-      <c r="K45" s="2">
+      <c r="K45" s="1">
         <v>-3.29999999999999</v>
       </c>
     </row>
@@ -1956,16 +2005,16 @@
       <c r="I46">
         <v>5</v>
       </c>
-      <c r="J46" s="2">
+      <c r="J46" s="1">
         <v>1.59999999999999</v>
       </c>
-      <c r="K46" s="2">
+      <c r="K46" s="1">
         <v>-3.79999999999999</v>
       </c>
     </row>
     <row r="47" spans="7:11">
       <c r="G47" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H47">
         <v>11</v>
@@ -1973,10 +2022,10 @@
       <c r="I47">
         <v>9</v>
       </c>
-      <c r="J47" s="2">
+      <c r="J47" s="1">
         <v>50.8</v>
       </c>
-      <c r="K47" s="2">
+      <c r="K47" s="1">
         <v>-28.5</v>
       </c>
     </row>
